--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T10:23:38+00:00</t>
+    <t>2025-02-24T13:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:55:23+00:00</t>
+    <t>2025-02-26T08:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T08:56:44+00:00</t>
+    <t>2025-03-04T11:06:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T11:06:18+00:00</t>
+    <t>2025-03-06T12:24:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T12:24:43+00:00</t>
+    <t>2025-03-20T12:28:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T12:28:15+00:00</t>
+    <t>2025-03-24T06:28:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-specimen</t>
+    <t>https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-specimen</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T06:28:05+00:00</t>
+    <t>2025-03-24T07:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -554,7 +554,7 @@
     <t>Specimen.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient)
 </t>
   </si>
   <si>
@@ -1423,7 +1423,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="89.3984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="69.87109375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T07:27:46+00:00</t>
+    <t>2025-03-24T07:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T10:23:29+00:00</t>
+    <t>2026-01-28T10:05:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -601,7 +601,7 @@
     <t>Specimen.parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-specimen)
 </t>
   </si>
   <si>
@@ -709,7 +709,7 @@
     <t>Specimen.collection.collector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole)
 </t>
   </si>
   <si>
@@ -1434,7 +1434,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="59.90234375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="120.3125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T10:05:57+00:00</t>
+    <t>2026-01-29T06:33:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T06:33:09+00:00</t>
+    <t>2026-02-03T10:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:06:44+00:00</t>
+    <t>2026-02-03T10:34:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:34:36+00:00</t>
+    <t>2026-02-09T07:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T07:50:08+00:00</t>
+    <t>2026-02-13T12:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T12:44:21+00:00</t>
+    <t>2026-02-16T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1073,7 +1073,7 @@
     <t>http://terminology.hl7.org/ValueSet/v2-0493</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T08:31:54+00:00</t>
+    <t>2026-02-16T11:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T11:13:42+00:00</t>
+    <t>2026-02-17T09:00:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-specimen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:00:43+00:00</t>
+    <t>2026-09-01T07:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -852,7 +852,7 @@
     <t>Codes describing the fasting status of the patient.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0916</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0916|3.0.0</t>
   </si>
   <si>
     <t>OBR-</t>
@@ -1043,7 +1043,7 @@
     <t>Substance added to specimen container.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0371</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0371|3.0.0</t>
   </si>
   <si>
     <t>.scopesRole[classCode=ADTV].player</t>
@@ -1070,7 +1070,7 @@
     <t>Codes describing the state of the specimen.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0493</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0493|3.0.0</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
